--- a/DesignerConfigs/Datas/PayoutStep.xlsx
+++ b/DesignerConfigs/Datas/PayoutStep.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="PayoutStep" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -62,6 +62,9 @@
     <t>explainLangId</t>
   </si>
   <si>
+    <t>finishLangId</t>
+  </si>
+  <si>
     <t>ifTerminal</t>
   </si>
   <si>
@@ -114,6 +117,9 @@
   </si>
   <si>
     <t>说明语言id</t>
+  </si>
+  <si>
+    <t>完成语言id</t>
   </si>
   <si>
     <t>是否终态</t>
@@ -129,14 +135,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -592,148 +591,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1088,7 +1087,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1096,11 +1095,13 @@
     <col min="5" max="5" width="13.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
     <col min="7" max="7" width="14.375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="14.5" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="8" max="11" width="14.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="14.5" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1134,130 +1135,142 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="L3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="B6" s="1">
         <v>1</v>
       </c>
@@ -1288,11 +1301,14 @@
       <c r="K6" s="1">
         <v>10204</v>
       </c>
-      <c r="L6" s="1" t="b">
+      <c r="L6">
+        <v>10238</v>
+      </c>
+      <c r="M6" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="B7" s="1">
         <v>2</v>
       </c>
@@ -1323,11 +1339,14 @@
       <c r="K7" s="1">
         <v>10208</v>
       </c>
-      <c r="L7" s="1" t="b">
+      <c r="L7">
+        <v>10239</v>
+      </c>
+      <c r="M7" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="B8" s="1">
         <v>3</v>
       </c>
@@ -1358,11 +1377,14 @@
       <c r="K8" s="1">
         <v>10212</v>
       </c>
-      <c r="L8" s="1" t="b">
+      <c r="L8">
+        <v>10240</v>
+      </c>
+      <c r="M8" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="B9" s="1">
         <v>4</v>
       </c>
@@ -1393,11 +1415,14 @@
       <c r="K9" s="1">
         <v>10216</v>
       </c>
-      <c r="L9" s="1" t="b">
+      <c r="L9">
+        <v>10241</v>
+      </c>
+      <c r="M9" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="B10" s="1">
         <v>5</v>
       </c>
@@ -1428,11 +1453,14 @@
       <c r="K10" s="1">
         <v>10220</v>
       </c>
-      <c r="L10" s="1" t="b">
+      <c r="L10">
+        <v>10242</v>
+      </c>
+      <c r="M10" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13">
       <c r="B11" s="1">
         <v>6</v>
       </c>
@@ -1463,11 +1491,14 @@
       <c r="K11" s="1">
         <v>10224</v>
       </c>
-      <c r="L11" s="1" t="b">
+      <c r="L11">
+        <v>10243</v>
+      </c>
+      <c r="M11" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:13">
       <c r="B12" s="1">
         <v>7</v>
       </c>
@@ -1498,11 +1529,14 @@
       <c r="K12" s="1">
         <v>10228</v>
       </c>
-      <c r="L12" s="1" t="b">
+      <c r="L12">
+        <v>10244</v>
+      </c>
+      <c r="M12" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:13">
       <c r="B13" s="1">
         <v>8</v>
       </c>
@@ -1533,7 +1567,10 @@
       <c r="K13" s="1">
         <v>10232</v>
       </c>
-      <c r="L13" s="1" t="b">
+      <c r="L13">
+        <v>10245</v>
+      </c>
+      <c r="M13" s="1" t="b">
         <v>1</v>
       </c>
     </row>

--- a/DesignerConfigs/Datas/PayoutStep.xlsx
+++ b/DesignerConfigs/Datas/PayoutStep.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="19710" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="PayoutStep" sheetId="1" r:id="rId1"/>
@@ -591,148 +591,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1090,15 +1090,15 @@
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="3" width="9" style="1"/>
+    <col min="1" max="3" width="9" style="1" customWidth="1"/>
     <col min="4" max="4" width="27.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
+    <col min="6" max="6" width="9" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.375" style="1" customWidth="1"/>
     <col min="8" max="11" width="14.5" style="1" customWidth="1"/>
     <col min="12" max="12" width="13.5" customWidth="1"/>
     <col min="13" max="13" width="14.5" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="14" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1354,16 +1354,16 @@
         <v>24</v>
       </c>
       <c r="D8" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
         <v>10209</v>
@@ -1389,13 +1389,13 @@
         <v>4</v>
       </c>
       <c r="C9" s="1">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D9" s="1">
         <v>3</v>
       </c>
       <c r="E9" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>

--- a/DesignerConfigs/Datas/PayoutStep.xlsx
+++ b/DesignerConfigs/Datas/PayoutStep.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19710" windowHeight="9060"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PayoutStep" sheetId="1" r:id="rId1"/>
